--- a/biblioteca/books.xlsx
+++ b/biblioteca/books.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\GitHub\biblioteca\biblioteca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55AB673-CAB2-4C5F-90DC-56DB0E4F209D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FCEEF4-E71A-4DDE-8F0B-2664B1E6E958}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
-    <x:workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="0" activeTab="0" xr2:uid="{C680D653-1AD1-4E20-9609-996EF76F5ACB}"/>
+    <x:workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="0" activeTab="0" xr2:uid="{C680D653-1AD1-4E20-9609-996EF76F5ACB}"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,6 @@
     <x:t>Robert C. Martin</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Programação </x:t>
-  </x:si>
-  <x:si>
     <x:t>The Pragmatic Programmer</x:t>
   </x:si>
   <x:si>
@@ -75,34 +72,34 @@
     <x:t>Eric Evans</x:t>
   </x:si>
   <x:si>
-    <x:t>Arquitetura de Software</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Refactoring </x:t>
   </x:si>
   <x:si>
     <x:t>Martin Fowler</x:t>
   </x:si>
   <x:si>
-    <x:t>Engenharia de Software</x:t>
-  </x:si>
-  <x:si>
     <x:t>Design Patterns</x:t>
   </x:si>
   <x:si>
     <x:t>Erich Gamma</x:t>
   </x:si>
   <x:si>
-    <x:t>Padrões de Projeto</x:t>
-  </x:si>
-  <x:si>
     <x:t>teste mm</x:t>
   </x:si>
   <x:si>
     <x:t>mm</x:t>
   </x:si>
   <x:si>
-    <x:t>programacao</x:t>
+    <x:t>Teste Aula Session 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anonimo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>oopo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ppp</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -470,7 +467,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G7"/>
+  <x:dimension ref="A1:G8"/>
   <x:sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <x:cols>
     <x:col min="1" max="1" width="9.179688" style="0" customWidth="1"/>
@@ -515,8 +512,8 @@
       <x:c r="C2" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>9</x:v>
+      <x:c r="D2" s="0">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>5</x:v>
@@ -533,13 +530,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>9</x:v>
+      <x:c r="D3" s="0">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>8</x:v>
@@ -556,13 +553,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="D4" s="0">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>6</x:v>
@@ -579,13 +576,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>3</x:v>
@@ -602,13 +599,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>7</x:v>
@@ -625,15 +622,15 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E7" s="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="1">
@@ -641,6 +638,52 @@
       </x:c>
       <x:c r="G7" s="1">
         <x:v>46074.4778570833</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <x:c r="A8" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D8" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="0">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F8" s="1">
+        <x:v>46079.8256130671</x:v>
+      </x:c>
+      <x:c r="G8" s="1">
+        <x:v>46086.4688904398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:7">
+      <x:c r="A9" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E9" s="0">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F9" s="1">
+        <x:v>46086.4609622222</x:v>
+      </x:c>
+      <x:c r="G9" s="1">
+        <x:v>46086.4686796412</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/biblioteca/books.xlsx
+++ b/biblioteca/books.xlsx
@@ -84,10 +84,10 @@
     <x:t>Erich Gamma</x:t>
   </x:si>
   <x:si>
-    <x:t>teste mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mm</x:t>
+    <x:t>Senhor dos aneis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senhor</x:t>
   </x:si>
   <x:si>
     <x:t>Teste Aula Session 2</x:t>
@@ -96,10 +96,25 @@
     <x:t>Anonimo</x:t>
   </x:si>
   <x:si>
-    <x:t>oopo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ppp</x:t>
+    <x:t>Novo Book</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Novo Autor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teste Book Categoria Exemplo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Autor Novo categoria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>uu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Livro new</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anonimo55</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -628,7 +643,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>10</x:v>
@@ -637,7 +652,7 @@
         <x:v>46074.4778570833</x:v>
       </x:c>
       <x:c r="G7" s="1">
-        <x:v>46074.4778570833</x:v>
+        <x:v>46086.785243669</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -683,7 +698,76 @@
         <x:v>46086.4609622222</x:v>
       </x:c>
       <x:c r="G9" s="1">
-        <x:v>46086.4686796412</x:v>
+        <x:v>46086.7846658333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:7">
+      <x:c r="A10" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E10" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F10" s="1">
+        <x:v>46086.8278061806</x:v>
+      </x:c>
+      <x:c r="G10" s="1">
+        <x:v>46086.8278062037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:7">
+      <x:c r="A11" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D11" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E11" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="1">
+        <x:v>46106.636874456</x:v>
+      </x:c>
+      <x:c r="G11" s="1">
+        <x:v>46106.6368744792</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:7">
+      <x:c r="A12" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D12" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E12" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F12" s="1">
+        <x:v>46107.8369597454</x:v>
+      </x:c>
+      <x:c r="G12" s="1">
+        <x:v>46107.8369597801</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
